--- a/财务与流水/馋唻买-听涛路店商品表 - 调价.xlsx
+++ b/财务与流水/馋唻买-听涛路店商品表 - 调价.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github localpath\ChanWeiMai\财务与流水\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD150D34-22B8-46D4-B91D-9E71C4E3C87D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E1FE97-8212-43F1-9CE1-15D481BE8461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1275" yWindow="915" windowWidth="35070" windowHeight="19335" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2475" yWindow="885" windowWidth="35070" windowHeight="19335" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="堂食利润" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="121">
   <si>
     <t>SKU</t>
   </si>
@@ -236,9 +236,6 @@
     <t>大份(240克)</t>
   </si>
   <si>
-    <t>10元</t>
-  </si>
-  <si>
     <t>本店招牌</t>
   </si>
   <si>
@@ -252,9 +249,6 @@
   </si>
   <si>
     <t>12元</t>
-  </si>
-  <si>
-    <t>16元</t>
   </si>
   <si>
     <t>牛肉羹瘦肉丸</t>
@@ -382,6 +376,22 @@
   </si>
   <si>
     <t>拌瘦肉丸(240g)</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>12元</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>16元</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>14元</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>18元</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -722,7 +732,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -732,9 +742,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -872,6 +879,10 @@
     </xf>
     <xf numFmtId="176" fontId="7" fillId="8" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1485,1566 +1496,1566 @@
   <dimension ref="A1:M39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="30.5" style="11" customWidth="1"/>
-    <col min="2" max="2" width="14" style="12" customWidth="1"/>
-    <col min="3" max="3" width="20.25" style="12" customWidth="1"/>
-    <col min="4" max="4" width="23.875" style="13" customWidth="1"/>
-    <col min="5" max="5" width="33.5" style="13" customWidth="1"/>
-    <col min="6" max="6" width="18.625" style="14" customWidth="1"/>
-    <col min="7" max="7" width="19.25" style="14" customWidth="1"/>
-    <col min="8" max="8" width="18.625" style="14" customWidth="1"/>
-    <col min="9" max="9" width="19.125" style="15" customWidth="1"/>
-    <col min="10" max="10" width="18" style="16" customWidth="1"/>
-    <col min="11" max="11" width="16.75" style="14" customWidth="1"/>
-    <col min="12" max="12" width="17.625" style="14" customWidth="1"/>
-    <col min="13" max="13" width="14.75" style="14" customWidth="1"/>
+    <col min="1" max="1" width="30.5" style="10" customWidth="1"/>
+    <col min="2" max="2" width="14" style="11" customWidth="1"/>
+    <col min="3" max="3" width="20.25" style="11" customWidth="1"/>
+    <col min="4" max="4" width="23.875" style="12" customWidth="1"/>
+    <col min="5" max="5" width="33.5" style="12" customWidth="1"/>
+    <col min="6" max="6" width="18.625" style="13" customWidth="1"/>
+    <col min="7" max="7" width="19.25" style="13" customWidth="1"/>
+    <col min="8" max="8" width="18.625" style="13" customWidth="1"/>
+    <col min="9" max="9" width="19.125" style="14" customWidth="1"/>
+    <col min="10" max="10" width="18" style="15" customWidth="1"/>
+    <col min="11" max="11" width="16.75" style="13" customWidth="1"/>
+    <col min="12" max="12" width="17.625" style="13" customWidth="1"/>
+    <col min="13" max="13" width="14.75" style="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" s="10" customFormat="1" ht="29.25" customHeight="1">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:13" s="9" customFormat="1" ht="29.25" customHeight="1">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="G1" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="26" t="s">
+      <c r="I1" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="31" t="s">
+      <c r="J1" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="26" t="s">
+      <c r="K1" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="26" t="s">
+      <c r="L1" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="26" t="s">
+      <c r="M1" s="25" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="21">
+      <c r="B2" s="20">
         <v>11</v>
       </c>
-      <c r="C2" s="21">
+      <c r="C2" s="20">
         <v>0.5</v>
       </c>
-      <c r="D2" s="22">
+      <c r="D2" s="21">
         <v>120</v>
       </c>
-      <c r="E2" s="27" t="s">
+      <c r="E2" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="28">
+      <c r="F2" s="27">
         <f>(B2+SKUTable[[#This Row],[运费(元/500g)]])*D2/500</f>
         <v>2.76</v>
       </c>
-      <c r="G2" s="28">
+      <c r="G2" s="27">
         <v>0.2</v>
       </c>
-      <c r="H2" s="28">
+      <c r="H2" s="27">
         <v>0.15</v>
       </c>
-      <c r="I2" s="32">
+      <c r="I2" s="31">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>3.11</v>
       </c>
-      <c r="J2" s="33">
+      <c r="J2" s="32">
         <v>6</v>
       </c>
-      <c r="K2" s="34">
+      <c r="K2" s="33">
         <f>J2-(F2+G2+H2)</f>
         <v>2.89</v>
       </c>
-      <c r="L2" s="34">
+      <c r="L2" s="33">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>92.926045016077168</v>
       </c>
-      <c r="M2" s="34">
+      <c r="M2" s="33">
         <f>(J2-(F2+G2+H2))/J2*100</f>
         <v>48.166666666666671</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="22">
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="21">
         <v>220</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="28">
+      <c r="F3" s="27">
         <v>2.4500000000000002</v>
       </c>
-      <c r="G3" s="28">
+      <c r="G3" s="27">
         <v>0.2</v>
       </c>
-      <c r="H3" s="28">
+      <c r="H3" s="27">
         <v>0.15</v>
       </c>
-      <c r="I3" s="32">
+      <c r="I3" s="31">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>2.8000000000000003</v>
       </c>
-      <c r="J3" s="33">
+      <c r="J3" s="32">
         <v>6</v>
       </c>
-      <c r="K3" s="34">
+      <c r="K3" s="33">
         <f>J3-(F3+G3+H3)</f>
         <v>3.1999999999999997</v>
       </c>
-      <c r="L3" s="34">
+      <c r="L3" s="33">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>114.28571428571426</v>
       </c>
-      <c r="M3" s="34">
+      <c r="M3" s="33">
         <f>(J3-(F3+G3+H3))/J3*100</f>
         <v>53.333333333333336</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="21">
+      <c r="B4" s="20">
         <v>8.8000000000000007</v>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="20">
         <v>0</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="21">
         <v>70</v>
       </c>
-      <c r="E4" s="27" t="s">
+      <c r="E4" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="27">
         <f>(B4+SKUTable[[#This Row],[运费(元/500g)]])*D4/500</f>
         <v>1.232</v>
       </c>
-      <c r="G4" s="28">
+      <c r="G4" s="27">
         <v>0.05</v>
       </c>
-      <c r="H4" s="28">
+      <c r="H4" s="27">
         <v>0</v>
       </c>
-      <c r="I4" s="32">
+      <c r="I4" s="31">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>1.282</v>
       </c>
-      <c r="J4" s="33">
+      <c r="J4" s="32">
         <v>4</v>
       </c>
-      <c r="K4" s="34">
+      <c r="K4" s="33">
         <f t="shared" ref="K4:K35" si="0">J4-(F4+G4+H4)</f>
         <v>2.718</v>
       </c>
-      <c r="L4" s="34">
+      <c r="L4" s="33">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>212.01248049921998</v>
       </c>
-      <c r="M4" s="34">
+      <c r="M4" s="33">
         <f t="shared" ref="M4:M35" si="1">(J4-(F4+G4+H4))/J4*100</f>
         <v>67.95</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="27">
         <v>1.3</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="27">
         <v>0.05</v>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="27">
         <v>0</v>
       </c>
-      <c r="I5" s="32">
+      <c r="I5" s="31">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>1.35</v>
       </c>
-      <c r="J5" s="33">
+      <c r="J5" s="32">
         <v>3</v>
       </c>
-      <c r="K5" s="34">
+      <c r="K5" s="33">
         <f t="shared" si="0"/>
         <v>1.65</v>
       </c>
-      <c r="L5" s="34">
+      <c r="L5" s="33">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>122.22222222222221</v>
       </c>
-      <c r="M5" s="34">
+      <c r="M5" s="33">
         <f t="shared" si="1"/>
         <v>54.999999999999993</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="27">
         <v>2.8</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="27">
         <v>0.05</v>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="27">
         <v>0</v>
       </c>
-      <c r="I6" s="32">
+      <c r="I6" s="31">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>2.8499999999999996</v>
       </c>
-      <c r="J6" s="33">
+      <c r="J6" s="32">
         <v>6</v>
       </c>
-      <c r="K6" s="34">
+      <c r="K6" s="33">
         <f t="shared" si="0"/>
         <v>3.1500000000000004</v>
       </c>
-      <c r="L6" s="34">
+      <c r="L6" s="33">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>110.52631578947371</v>
       </c>
-      <c r="M6" s="34">
+      <c r="M6" s="33">
         <f t="shared" si="1"/>
         <v>52.5</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="21" t="s">
+      <c r="C7" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="28">
         <v>3.24</v>
       </c>
-      <c r="G7" s="29">
+      <c r="G7" s="28">
         <v>0.2</v>
       </c>
-      <c r="H7" s="29">
+      <c r="H7" s="28">
         <v>0</v>
       </c>
-      <c r="I7" s="35">
+      <c r="I7" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>3.4400000000000004</v>
       </c>
-      <c r="J7" s="29">
+      <c r="J7" s="28">
         <v>8</v>
       </c>
-      <c r="K7" s="36">
+      <c r="K7" s="35">
         <f t="shared" si="0"/>
         <v>4.5599999999999996</v>
       </c>
-      <c r="L7" s="36">
+      <c r="L7" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>132.55813953488368</v>
       </c>
-      <c r="M7" s="36">
+      <c r="M7" s="35">
         <f t="shared" si="1"/>
         <v>56.999999999999993</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A8" s="23" t="s">
+      <c r="A8" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="C8" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="28">
         <v>0.4</v>
       </c>
-      <c r="G8" s="29">
+      <c r="G8" s="28">
         <v>0</v>
       </c>
-      <c r="H8" s="29">
+      <c r="H8" s="28">
         <v>0</v>
       </c>
-      <c r="I8" s="35">
+      <c r="I8" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>0.4</v>
       </c>
-      <c r="J8" s="29">
+      <c r="J8" s="28">
         <v>1.25</v>
       </c>
-      <c r="K8" s="36">
+      <c r="K8" s="35">
         <f t="shared" si="0"/>
         <v>0.85</v>
       </c>
-      <c r="L8" s="36">
+      <c r="L8" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>212.5</v>
       </c>
-      <c r="M8" s="36">
+      <c r="M8" s="35">
         <f t="shared" si="1"/>
         <v>68</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A9" s="20" t="s">
+      <c r="A9" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="27" t="s">
+      <c r="E9" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="28">
         <v>0.45</v>
       </c>
-      <c r="G9" s="29">
+      <c r="G9" s="28">
         <v>0</v>
       </c>
-      <c r="H9" s="29">
+      <c r="H9" s="28">
         <v>0</v>
       </c>
-      <c r="I9" s="35">
+      <c r="I9" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>0.45</v>
       </c>
-      <c r="J9" s="29">
+      <c r="J9" s="28">
         <v>1.25</v>
       </c>
-      <c r="K9" s="36">
+      <c r="K9" s="35">
         <f t="shared" si="0"/>
         <v>0.8</v>
       </c>
-      <c r="L9" s="36">
+      <c r="L9" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>177.7777777777778</v>
       </c>
-      <c r="M9" s="36">
+      <c r="M9" s="35">
         <f t="shared" si="1"/>
         <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="28">
         <v>1.37</v>
       </c>
-      <c r="G10" s="29">
+      <c r="G10" s="28">
         <v>0</v>
       </c>
-      <c r="H10" s="29">
+      <c r="H10" s="28">
         <v>0</v>
       </c>
-      <c r="I10" s="35">
+      <c r="I10" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>1.37</v>
       </c>
-      <c r="J10" s="29">
+      <c r="J10" s="28">
         <v>2.5</v>
       </c>
-      <c r="K10" s="36">
+      <c r="K10" s="35">
         <f t="shared" si="0"/>
         <v>1.1299999999999999</v>
       </c>
-      <c r="L10" s="36">
+      <c r="L10" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>82.481751824817508</v>
       </c>
-      <c r="M10" s="36">
+      <c r="M10" s="35">
         <f t="shared" si="1"/>
         <v>45.199999999999996</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A11" s="20" t="s">
+      <c r="A11" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="D11" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="E11" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="29">
+      <c r="F11" s="28">
         <v>1.37</v>
       </c>
-      <c r="G11" s="29">
+      <c r="G11" s="28">
         <v>0</v>
       </c>
-      <c r="H11" s="29">
+      <c r="H11" s="28">
         <v>0</v>
       </c>
-      <c r="I11" s="35">
+      <c r="I11" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>1.37</v>
       </c>
-      <c r="J11" s="29">
+      <c r="J11" s="28">
         <v>2.5</v>
       </c>
-      <c r="K11" s="36">
+      <c r="K11" s="35">
         <f t="shared" si="0"/>
         <v>1.1299999999999999</v>
       </c>
-      <c r="L11" s="36">
+      <c r="L11" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>82.481751824817508</v>
       </c>
-      <c r="M11" s="36">
+      <c r="M11" s="35">
         <f t="shared" si="1"/>
         <v>45.199999999999996</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="B12" s="21">
+      <c r="B12" s="20">
         <v>8</v>
       </c>
-      <c r="C12" s="21">
+      <c r="C12" s="20">
         <v>0.5</v>
       </c>
-      <c r="D12" s="22">
+      <c r="D12" s="21">
         <v>165</v>
       </c>
-      <c r="E12" s="27" t="s">
+      <c r="E12" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="28">
         <f>(B12+SKUTable[[#This Row],[运费(元/500g)]])*D12/500</f>
         <v>2.8050000000000002</v>
       </c>
-      <c r="G12" s="29">
+      <c r="G12" s="28">
         <v>0.68500000000000005</v>
       </c>
-      <c r="H12" s="29">
+      <c r="H12" s="28">
         <v>0.2</v>
       </c>
-      <c r="I12" s="35">
+      <c r="I12" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>3.6900000000000004</v>
       </c>
-      <c r="J12" s="29">
-        <v>10</v>
-      </c>
-      <c r="K12" s="36">
+      <c r="J12" s="28">
+        <v>12</v>
+      </c>
+      <c r="K12" s="35">
         <f t="shared" si="0"/>
-        <v>6.31</v>
-      </c>
-      <c r="L12" s="36">
+        <v>8.3099999999999987</v>
+      </c>
+      <c r="L12" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>171.00271002710025</v>
-      </c>
-      <c r="M12" s="36">
+        <v>225.20325203252028</v>
+      </c>
+      <c r="M12" s="35">
         <f t="shared" si="1"/>
-        <v>63.1</v>
+        <v>69.249999999999986</v>
       </c>
     </row>
     <row r="13" spans="1:13" ht="20.25" customHeight="1">
-      <c r="A13" s="20" t="s">
+      <c r="A13" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="21">
+      <c r="B13" s="20">
         <v>8</v>
       </c>
-      <c r="C13" s="21">
+      <c r="C13" s="20">
         <v>0.5</v>
       </c>
-      <c r="D13" s="22">
+      <c r="D13" s="21">
         <v>260</v>
       </c>
-      <c r="E13" s="27" t="s">
+      <c r="E13" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="F13" s="29">
+      <c r="F13" s="28">
         <f>(B13+SKUTable[[#This Row],[运费(元/500g)]])*D13/500</f>
         <v>4.42</v>
       </c>
-      <c r="G13" s="29">
+      <c r="G13" s="28">
         <v>0.82</v>
       </c>
-      <c r="H13" s="29">
+      <c r="H13" s="28">
         <v>0.2</v>
       </c>
-      <c r="I13" s="35">
+      <c r="I13" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>5.44</v>
       </c>
-      <c r="J13" s="29">
-        <v>15</v>
-      </c>
-      <c r="K13" s="36">
+      <c r="J13" s="28">
+        <v>16</v>
+      </c>
+      <c r="K13" s="35">
         <f t="shared" si="0"/>
-        <v>9.5599999999999987</v>
-      </c>
-      <c r="L13" s="36">
+        <v>10.559999999999999</v>
+      </c>
+      <c r="L13" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>175.73529411764702</v>
-      </c>
-      <c r="M13" s="36">
+        <v>194.11764705882348</v>
+      </c>
+      <c r="M13" s="35">
         <f t="shared" si="1"/>
-        <v>63.73333333333332</v>
+        <v>65.999999999999986</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="21">
+      <c r="B14" s="20">
         <v>10</v>
       </c>
-      <c r="C14" s="21">
+      <c r="C14" s="20">
         <v>0.5</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="21">
         <v>165</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="28">
         <f>IF(B14&lt;&gt;"",B14*D14/500,"")</f>
         <v>3.3</v>
       </c>
-      <c r="G14" s="29">
+      <c r="G14" s="28">
         <v>0.68500000000000005</v>
       </c>
-      <c r="H14" s="29">
+      <c r="H14" s="28">
         <v>0.2</v>
       </c>
-      <c r="I14" s="35">
+      <c r="I14" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>4.1849999999999996</v>
       </c>
-      <c r="J14" s="29">
-        <v>12</v>
-      </c>
-      <c r="K14" s="36">
+      <c r="J14" s="28">
+        <v>14</v>
+      </c>
+      <c r="K14" s="35">
         <f t="shared" si="0"/>
-        <v>7.8150000000000004</v>
-      </c>
-      <c r="L14" s="36">
+        <v>9.8150000000000013</v>
+      </c>
+      <c r="L14" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>186.73835125448031</v>
-      </c>
-      <c r="M14" s="36">
+        <v>234.52807646356041</v>
+      </c>
+      <c r="M14" s="35">
         <f t="shared" si="1"/>
-        <v>65.125</v>
+        <v>70.107142857142861</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="21">
+      <c r="B15" s="20">
         <v>10</v>
       </c>
-      <c r="C15" s="21">
+      <c r="C15" s="20">
         <v>0.5</v>
       </c>
-      <c r="D15" s="22">
+      <c r="D15" s="21">
         <v>260</v>
       </c>
-      <c r="E15" s="27" t="s">
+      <c r="E15" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="28">
         <f>IF(B15&lt;&gt;"",B15*D15/500,"")</f>
         <v>5.2</v>
       </c>
-      <c r="G15" s="29">
+      <c r="G15" s="28">
         <v>0.82</v>
       </c>
-      <c r="H15" s="29">
+      <c r="H15" s="28">
         <v>0.2</v>
       </c>
-      <c r="I15" s="35">
+      <c r="I15" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>6.2200000000000006</v>
       </c>
-      <c r="J15" s="29">
-        <v>16</v>
-      </c>
-      <c r="K15" s="36">
+      <c r="J15" s="28">
+        <v>18</v>
+      </c>
+      <c r="K15" s="35">
         <f t="shared" si="0"/>
-        <v>9.7799999999999994</v>
-      </c>
-      <c r="L15" s="36">
+        <v>11.78</v>
+      </c>
+      <c r="L15" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
-        <v>157.23472668810288</v>
-      </c>
-      <c r="M15" s="36">
+        <v>189.38906752411572</v>
+      </c>
+      <c r="M15" s="35">
         <f t="shared" si="1"/>
-        <v>61.124999999999993</v>
+        <v>65.444444444444443</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="22" t="s">
         <v>38</v>
       </c>
-      <c r="B16" s="21">
+      <c r="B16" s="20">
         <v>17</v>
       </c>
-      <c r="C16" s="21">
+      <c r="C16" s="20">
         <v>0.5</v>
       </c>
-      <c r="D16" s="22">
+      <c r="D16" s="21">
         <v>135</v>
       </c>
-      <c r="E16" s="27" t="s">
+      <c r="E16" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="28">
         <f t="shared" ref="F16" si="2">IF(B16&lt;&gt;"",B16*D16/500,"")</f>
         <v>4.59</v>
       </c>
-      <c r="G16" s="29">
+      <c r="G16" s="28">
         <v>0.68500000000000005</v>
       </c>
-      <c r="H16" s="29">
+      <c r="H16" s="28">
         <v>0.2</v>
       </c>
-      <c r="I16" s="35">
+      <c r="I16" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>5.4750000000000005</v>
       </c>
-      <c r="J16" s="29"/>
-      <c r="K16" s="36">
+      <c r="J16" s="28"/>
+      <c r="K16" s="35">
         <f t="shared" ref="K16" si="3">J16-(F16+G16+H16)</f>
         <v>-5.4750000000000005</v>
       </c>
-      <c r="L16" s="36">
+      <c r="L16" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>-100</v>
       </c>
-      <c r="M16" s="36" t="e">
+      <c r="M16" s="35" t="e">
         <f t="shared" ref="M16" si="4">(J16-(F16+G16+H16))/J16*100</f>
         <v>#DIV/0!</v>
       </c>
     </row>
     <row r="17" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A17" s="23" t="s">
+      <c r="A17" s="22" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="21">
+      <c r="B17" s="20">
         <v>17</v>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="20">
         <v>0.5</v>
       </c>
-      <c r="D17" s="22">
+      <c r="D17" s="21">
         <v>165</v>
       </c>
-      <c r="E17" s="27" t="s">
+      <c r="E17" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="F17" s="29">
+      <c r="F17" s="28">
         <f t="shared" ref="F17:F34" si="5">IF(B17&lt;&gt;"",B17*D17/500,"")</f>
         <v>5.61</v>
       </c>
-      <c r="G17" s="29">
+      <c r="G17" s="28">
         <v>0.68500000000000005</v>
       </c>
-      <c r="H17" s="29">
+      <c r="H17" s="28">
         <v>0.2</v>
       </c>
-      <c r="I17" s="35">
+      <c r="I17" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>6.4950000000000001</v>
       </c>
-      <c r="J17" s="29">
+      <c r="J17" s="28">
         <v>15</v>
       </c>
-      <c r="K17" s="36">
+      <c r="K17" s="35">
         <f t="shared" si="0"/>
         <v>8.504999999999999</v>
       </c>
-      <c r="L17" s="36">
+      <c r="L17" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>130.94688221709006</v>
       </c>
-      <c r="M17" s="36">
+      <c r="M17" s="35">
         <f t="shared" si="1"/>
         <v>56.699999999999996</v>
       </c>
     </row>
     <row r="18" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A18" s="23" t="s">
+      <c r="A18" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="21">
+      <c r="B18" s="20">
         <v>17</v>
       </c>
-      <c r="C18" s="21">
+      <c r="C18" s="20">
         <v>0.5</v>
       </c>
-      <c r="D18" s="22">
+      <c r="D18" s="21">
         <v>260</v>
       </c>
-      <c r="E18" s="27" t="s">
+      <c r="E18" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="F18" s="29">
+      <c r="F18" s="28">
         <f t="shared" si="5"/>
         <v>8.84</v>
       </c>
-      <c r="G18" s="29">
+      <c r="G18" s="28">
         <v>0.82</v>
       </c>
-      <c r="H18" s="29">
+      <c r="H18" s="28">
         <v>0.2</v>
       </c>
-      <c r="I18" s="35">
+      <c r="I18" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>9.86</v>
       </c>
-      <c r="J18" s="29">
+      <c r="J18" s="28">
         <v>20</v>
       </c>
-      <c r="K18" s="36">
+      <c r="K18" s="35">
         <f t="shared" si="0"/>
         <v>10.14</v>
       </c>
-      <c r="L18" s="36">
+      <c r="L18" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>102.8397565922921</v>
       </c>
-      <c r="M18" s="36">
+      <c r="M18" s="35">
         <f t="shared" si="1"/>
         <v>50.7</v>
       </c>
     </row>
     <row r="19" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A19" s="40" t="s">
+      <c r="A19" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="B19" s="25">
+      <c r="B19" s="24">
         <v>18</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="24">
         <v>0.5</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="23">
         <v>100</v>
       </c>
-      <c r="E19" s="56" t="s">
+      <c r="E19" s="55" t="s">
         <v>43</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="29">
         <f t="shared" si="5"/>
         <v>3.6</v>
       </c>
-      <c r="G19" s="30">
+      <c r="G19" s="29">
         <v>0.68500000000000005</v>
       </c>
-      <c r="H19" s="30">
+      <c r="H19" s="29">
         <v>0.2</v>
       </c>
-      <c r="I19" s="37">
+      <c r="I19" s="36">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>4.4850000000000003</v>
       </c>
-      <c r="J19" s="30">
+      <c r="J19" s="29">
         <v>10</v>
       </c>
-      <c r="K19" s="57">
+      <c r="K19" s="56">
         <f t="shared" si="0"/>
         <v>5.5149999999999997</v>
       </c>
-      <c r="L19" s="57">
+      <c r="L19" s="56">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>122.96544035674468</v>
       </c>
-      <c r="M19" s="57">
+      <c r="M19" s="56">
         <f t="shared" si="1"/>
         <v>55.15</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A20" s="40" t="s">
-        <v>115</v>
-      </c>
-      <c r="B20" s="21">
+      <c r="A20" s="39" t="s">
+        <v>113</v>
+      </c>
+      <c r="B20" s="20">
         <v>18</v>
       </c>
-      <c r="C20" s="21">
+      <c r="C20" s="20">
         <v>0.5</v>
       </c>
-      <c r="D20" s="22">
+      <c r="D20" s="21">
         <v>135</v>
       </c>
-      <c r="E20" s="27" t="s">
+      <c r="E20" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="F20" s="29">
+      <c r="F20" s="28">
         <f t="shared" ref="F20" si="6">IF(B20&lt;&gt;"",B20*D20/500,"")</f>
         <v>4.8600000000000003</v>
       </c>
-      <c r="G20" s="29">
+      <c r="G20" s="28">
         <v>0.68500000000000005</v>
       </c>
-      <c r="H20" s="29">
+      <c r="H20" s="28">
         <v>0.2</v>
       </c>
-      <c r="I20" s="35">
+      <c r="I20" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>5.7450000000000001</v>
       </c>
-      <c r="J20" s="29">
+      <c r="J20" s="28">
         <v>15</v>
       </c>
-      <c r="K20" s="36">
+      <c r="K20" s="35">
         <f t="shared" ref="K20" si="7">J20-(F20+G20+H20)</f>
         <v>9.254999999999999</v>
       </c>
-      <c r="L20" s="36">
+      <c r="L20" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>161.0966057441253</v>
       </c>
-      <c r="M20" s="36">
+      <c r="M20" s="35">
         <f t="shared" ref="M20" si="8">(J20-(F20+G20+H20))/J20*100</f>
         <v>61.699999999999989</v>
       </c>
     </row>
     <row r="21" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="B21" s="21">
+      <c r="B21" s="20">
         <v>19</v>
       </c>
-      <c r="C21" s="21">
+      <c r="C21" s="20">
         <v>0.5</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="E21" s="27" t="s">
+      <c r="E21" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="F21" s="29"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="29"/>
-      <c r="I21" s="35"/>
-      <c r="J21" s="29"/>
-      <c r="K21" s="36"/>
-      <c r="L21" s="36"/>
-      <c r="M21" s="36"/>
+      <c r="F21" s="28"/>
+      <c r="G21" s="28"/>
+      <c r="H21" s="28"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="28"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="35"/>
+      <c r="M21" s="35"/>
     </row>
     <row r="22" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A22" s="23" t="s">
+      <c r="A22" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B22" s="21">
+      <c r="B22" s="20">
         <v>19</v>
       </c>
-      <c r="C22" s="21">
+      <c r="C22" s="20">
         <v>0.5</v>
       </c>
-      <c r="D22" s="22">
+      <c r="D22" s="21">
         <v>90</v>
       </c>
-      <c r="E22" s="27" t="s">
+      <c r="E22" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="F22" s="29">
+      <c r="F22" s="28">
         <f t="shared" si="5"/>
         <v>3.42</v>
       </c>
-      <c r="G22" s="29"/>
-      <c r="H22" s="29">
+      <c r="G22" s="28"/>
+      <c r="H22" s="28">
         <v>2.5</v>
       </c>
-      <c r="I22" s="35">
+      <c r="I22" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>5.92</v>
       </c>
-      <c r="J22" s="29">
+      <c r="J22" s="28">
         <v>13</v>
       </c>
-      <c r="K22" s="36">
+      <c r="K22" s="35">
         <f t="shared" si="0"/>
         <v>7.08</v>
       </c>
-      <c r="L22" s="36">
+      <c r="L22" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>119.59459459459461</v>
       </c>
-      <c r="M22" s="36">
+      <c r="M22" s="35">
         <f t="shared" si="1"/>
         <v>54.46153846153846</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A23" s="23" t="s">
+      <c r="A23" s="22" t="s">
         <v>47</v>
       </c>
-      <c r="B23" s="21">
+      <c r="B23" s="20">
         <v>19</v>
       </c>
-      <c r="C23" s="21">
+      <c r="C23" s="20">
         <v>0.5</v>
       </c>
-      <c r="D23" s="22">
+      <c r="D23" s="21">
         <v>70</v>
       </c>
-      <c r="E23" s="27" t="s">
+      <c r="E23" s="26" t="s">
         <v>46</v>
       </c>
-      <c r="F23" s="29">
+      <c r="F23" s="28">
         <f t="shared" si="5"/>
         <v>2.66</v>
       </c>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29">
+      <c r="G23" s="28"/>
+      <c r="H23" s="28">
         <v>2.5</v>
       </c>
-      <c r="I23" s="35">
+      <c r="I23" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>5.16</v>
       </c>
-      <c r="J23" s="29">
+      <c r="J23" s="28">
         <v>13</v>
       </c>
-      <c r="K23" s="36">
+      <c r="K23" s="35">
         <f t="shared" si="0"/>
         <v>7.84</v>
       </c>
-      <c r="L23" s="36">
+      <c r="L23" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>151.93798449612405</v>
       </c>
-      <c r="M23" s="36">
+      <c r="M23" s="35">
         <f t="shared" si="1"/>
         <v>60.307692307692307</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A24" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="B24" s="21">
+      <c r="A24" s="39" t="s">
+        <v>116</v>
+      </c>
+      <c r="B24" s="20">
         <v>8</v>
       </c>
-      <c r="C24" s="21">
+      <c r="C24" s="20">
         <v>0.5</v>
       </c>
-      <c r="D24" s="22">
+      <c r="D24" s="21">
         <v>165</v>
       </c>
-      <c r="E24" s="27" t="s">
+      <c r="E24" s="26" t="s">
         <v>33</v>
       </c>
-      <c r="F24" s="29">
+      <c r="F24" s="28">
         <f t="shared" si="5"/>
         <v>2.64</v>
       </c>
-      <c r="G24" s="29">
+      <c r="G24" s="28">
         <v>0.82</v>
       </c>
-      <c r="H24" s="30">
+      <c r="H24" s="29">
         <v>0.5</v>
       </c>
-      <c r="I24" s="37">
+      <c r="I24" s="36">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>3.96</v>
       </c>
-      <c r="J24" s="29">
+      <c r="J24" s="28">
         <v>15</v>
       </c>
-      <c r="K24" s="36">
+      <c r="K24" s="35">
         <f t="shared" si="0"/>
         <v>11.04</v>
       </c>
-      <c r="L24" s="36">
+      <c r="L24" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>278.78787878787875</v>
       </c>
-      <c r="M24" s="36">
+      <c r="M24" s="35">
         <f t="shared" si="1"/>
         <v>73.599999999999994</v>
       </c>
     </row>
     <row r="25" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A25" s="41" t="s">
+      <c r="A25" s="40" t="s">
         <v>48</v>
       </c>
-      <c r="B25" s="42">
+      <c r="B25" s="41">
         <v>9.09</v>
       </c>
-      <c r="C25" s="42">
+      <c r="C25" s="41">
         <v>0.5</v>
       </c>
-      <c r="D25" s="43">
+      <c r="D25" s="42">
         <v>165</v>
       </c>
-      <c r="E25" s="43" t="s">
+      <c r="E25" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="F25" s="44">
+      <c r="F25" s="43">
         <f t="shared" si="5"/>
         <v>2.9996999999999998</v>
       </c>
-      <c r="G25" s="44">
+      <c r="G25" s="43">
         <v>0.68500000000000005</v>
       </c>
-      <c r="H25" s="45">
+      <c r="H25" s="44">
         <v>1.5</v>
       </c>
-      <c r="I25" s="46">
+      <c r="I25" s="45">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>5.1846999999999994</v>
       </c>
-      <c r="J25" s="44">
+      <c r="J25" s="43">
         <v>14</v>
       </c>
-      <c r="K25" s="47">
+      <c r="K25" s="46">
         <f t="shared" si="0"/>
         <v>8.8153000000000006</v>
       </c>
-      <c r="L25" s="47">
+      <c r="L25" s="46">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>170.02526664995085</v>
       </c>
-      <c r="M25" s="47">
+      <c r="M25" s="46">
         <f t="shared" si="1"/>
         <v>62.96642857142858</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A26" s="41" t="s">
+      <c r="A26" s="40" t="s">
         <v>50</v>
       </c>
-      <c r="B26" s="42">
+      <c r="B26" s="41">
         <v>9.09</v>
       </c>
-      <c r="C26" s="42">
+      <c r="C26" s="41">
         <v>0.5</v>
       </c>
-      <c r="D26" s="43">
+      <c r="D26" s="42">
         <v>260</v>
       </c>
-      <c r="E26" s="43" t="s">
+      <c r="E26" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="F26" s="44">
+      <c r="F26" s="43">
         <f t="shared" si="5"/>
         <v>4.7267999999999999</v>
       </c>
-      <c r="G26" s="44">
+      <c r="G26" s="43">
         <v>0.82</v>
       </c>
-      <c r="H26" s="45">
+      <c r="H26" s="44">
         <v>1.5</v>
       </c>
-      <c r="I26" s="46">
+      <c r="I26" s="45">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>7.0468000000000002</v>
       </c>
-      <c r="J26" s="44">
+      <c r="J26" s="43">
         <v>18</v>
       </c>
-      <c r="K26" s="47">
+      <c r="K26" s="46">
         <f t="shared" si="0"/>
         <v>10.953199999999999</v>
       </c>
-      <c r="L26" s="47">
+      <c r="L26" s="46">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>155.43509110518247</v>
       </c>
-      <c r="M26" s="47">
+      <c r="M26" s="46">
         <f t="shared" si="1"/>
         <v>60.851111111111102</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A27" s="20" t="s">
+      <c r="A27" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="B27" s="21">
+      <c r="B27" s="20">
         <v>11.75</v>
       </c>
-      <c r="C27" s="21" t="s">
+      <c r="C27" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="22">
+      <c r="D27" s="21">
         <v>35</v>
       </c>
-      <c r="E27" s="22"/>
-      <c r="F27" s="29">
+      <c r="E27" s="21"/>
+      <c r="F27" s="28">
         <f t="shared" si="5"/>
         <v>0.82250000000000001</v>
       </c>
-      <c r="G27" s="29" t="s">
+      <c r="G27" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="H27" s="30" t="s">
+      <c r="H27" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="I27" s="37">
+      <c r="I27" s="36">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>0.82250000000000001</v>
       </c>
-      <c r="J27" s="29" t="s">
+      <c r="J27" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="K27" s="36" t="s">
+      <c r="K27" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="L27" s="36"/>
-      <c r="M27" s="36" t="s">
+      <c r="L27" s="35"/>
+      <c r="M27" s="35" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A28" s="20" t="s">
+      <c r="A28" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="B28" s="21">
+      <c r="B28" s="20">
         <v>8</v>
       </c>
-      <c r="C28" s="21">
+      <c r="C28" s="20">
         <v>0.5</v>
       </c>
-      <c r="D28" s="22">
+      <c r="D28" s="21">
         <v>165</v>
       </c>
-      <c r="E28" s="27" t="s">
+      <c r="E28" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="F28" s="29">
+      <c r="F28" s="28">
         <f t="shared" si="5"/>
         <v>2.64</v>
       </c>
-      <c r="G28" s="29">
+      <c r="G28" s="28">
         <v>0.68500000000000005</v>
       </c>
-      <c r="H28" s="30">
+      <c r="H28" s="29">
         <v>1.2</v>
       </c>
-      <c r="I28" s="37">
+      <c r="I28" s="36">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>4.5250000000000004</v>
       </c>
-      <c r="J28" s="29">
+      <c r="J28" s="28">
         <v>15</v>
       </c>
-      <c r="K28" s="36">
+      <c r="K28" s="35">
         <f t="shared" si="0"/>
         <v>10.475</v>
       </c>
-      <c r="L28" s="36">
+      <c r="L28" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>231.49171270718227</v>
       </c>
-      <c r="M28" s="36">
+      <c r="M28" s="35">
         <f t="shared" si="1"/>
         <v>69.833333333333343</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A29" s="41" t="s">
+      <c r="A29" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="B29" s="42">
+      <c r="B29" s="41">
         <v>8</v>
       </c>
-      <c r="C29" s="42">
+      <c r="C29" s="41">
         <v>0.5</v>
       </c>
-      <c r="D29" s="43">
+      <c r="D29" s="42">
         <v>260</v>
       </c>
-      <c r="E29" s="43" t="s">
+      <c r="E29" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="F29" s="44">
+      <c r="F29" s="43">
         <f t="shared" si="5"/>
         <v>4.16</v>
       </c>
-      <c r="G29" s="44">
+      <c r="G29" s="43">
         <v>0.82</v>
       </c>
-      <c r="H29" s="45">
+      <c r="H29" s="44">
         <v>1.2</v>
       </c>
-      <c r="I29" s="46">
+      <c r="I29" s="45">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>6.1800000000000006</v>
       </c>
-      <c r="J29" s="44">
+      <c r="J29" s="43">
         <v>18</v>
       </c>
-      <c r="K29" s="47">
+      <c r="K29" s="46">
         <f t="shared" si="0"/>
         <v>11.82</v>
       </c>
-      <c r="L29" s="47">
+      <c r="L29" s="46">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>191.26213592233009</v>
       </c>
-      <c r="M29" s="47">
+      <c r="M29" s="46">
         <f t="shared" si="1"/>
         <v>65.666666666666671</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A30" s="20" t="s">
+      <c r="A30" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="B30" s="21">
+      <c r="B30" s="20">
         <v>2.875</v>
       </c>
-      <c r="C30" s="21" t="s">
+      <c r="C30" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="24">
+      <c r="D30" s="23">
         <v>140</v>
       </c>
-      <c r="E30" s="27" t="s">
+      <c r="E30" s="26" t="s">
         <v>56</v>
       </c>
-      <c r="F30" s="29">
+      <c r="F30" s="28">
         <f t="shared" si="5"/>
         <v>0.80500000000000005</v>
       </c>
-      <c r="G30" s="29">
+      <c r="G30" s="28">
         <v>0.82</v>
       </c>
-      <c r="H30" s="29">
+      <c r="H30" s="28">
         <v>4.0999999999999996</v>
       </c>
-      <c r="I30" s="35">
+      <c r="I30" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>5.7249999999999996</v>
       </c>
-      <c r="J30" s="29">
+      <c r="J30" s="28">
         <v>15</v>
       </c>
-      <c r="K30" s="36">
+      <c r="K30" s="35">
         <f t="shared" si="0"/>
         <v>9.2750000000000004</v>
       </c>
-      <c r="L30" s="36">
+      <c r="L30" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>162.00873362445415</v>
       </c>
-      <c r="M30" s="36">
+      <c r="M30" s="35">
         <f t="shared" si="1"/>
         <v>61.833333333333343</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A31" s="48" t="s">
-        <v>116</v>
-      </c>
-      <c r="B31" s="21"/>
-      <c r="C31" s="21">
+      <c r="A31" s="47" t="s">
+        <v>114</v>
+      </c>
+      <c r="B31" s="20"/>
+      <c r="C31" s="20">
         <v>0.5</v>
       </c>
-      <c r="D31" s="22"/>
-      <c r="E31" s="27" t="s">
+      <c r="D31" s="21"/>
+      <c r="E31" s="26" t="s">
         <v>57</v>
       </c>
-      <c r="F31" s="29">
+      <c r="F31" s="28">
         <v>6.11</v>
       </c>
-      <c r="G31" s="29">
+      <c r="G31" s="28">
         <v>0.68500000000000005</v>
       </c>
-      <c r="H31" s="29">
+      <c r="H31" s="28">
         <v>0.2</v>
       </c>
-      <c r="I31" s="35">
+      <c r="I31" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>6.9950000000000001</v>
       </c>
-      <c r="J31" s="29">
+      <c r="J31" s="28">
         <v>20</v>
       </c>
-      <c r="K31" s="36">
+      <c r="K31" s="35">
         <f t="shared" si="0"/>
         <v>13.004999999999999</v>
       </c>
-      <c r="L31" s="36">
+      <c r="L31" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>185.91851322373122</v>
       </c>
-      <c r="M31" s="36">
+      <c r="M31" s="35">
         <f t="shared" si="1"/>
         <v>65.025000000000006</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A32" s="49" t="s">
-        <v>117</v>
-      </c>
-      <c r="B32" s="50"/>
-      <c r="C32" s="50">
+      <c r="A32" s="48" t="s">
+        <v>115</v>
+      </c>
+      <c r="B32" s="49"/>
+      <c r="C32" s="49">
         <v>0.5</v>
       </c>
-      <c r="D32" s="51"/>
-      <c r="E32" s="52" t="s">
+      <c r="D32" s="50"/>
+      <c r="E32" s="51" t="s">
         <v>58</v>
       </c>
-      <c r="F32" s="53">
+      <c r="F32" s="52">
         <v>8.32</v>
       </c>
-      <c r="G32" s="53">
+      <c r="G32" s="52">
         <v>0.68500000000000005</v>
       </c>
-      <c r="H32" s="53">
+      <c r="H32" s="52">
         <v>0.2</v>
       </c>
-      <c r="I32" s="54">
+      <c r="I32" s="53">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>9.2050000000000001</v>
       </c>
-      <c r="J32" s="53">
+      <c r="J32" s="52">
         <v>20</v>
       </c>
-      <c r="K32" s="55">
+      <c r="K32" s="54">
         <f t="shared" si="0"/>
         <v>10.795</v>
       </c>
-      <c r="L32" s="55">
+      <c r="L32" s="54">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>117.27322107550245</v>
       </c>
-      <c r="M32" s="55">
+      <c r="M32" s="54">
         <f t="shared" si="1"/>
         <v>53.974999999999994</v>
       </c>
     </row>
     <row r="33" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A33" s="20" t="s">
+      <c r="A33" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21">
+      <c r="B33" s="20"/>
+      <c r="C33" s="20">
         <v>0.5</v>
       </c>
-      <c r="D33" s="22">
+      <c r="D33" s="21">
         <v>370</v>
       </c>
-      <c r="E33" s="27" t="s">
+      <c r="E33" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="F33" s="29">
+      <c r="F33" s="28">
         <v>6.64</v>
       </c>
-      <c r="G33" s="29">
+      <c r="G33" s="28">
         <v>0.82</v>
       </c>
-      <c r="H33" s="29">
+      <c r="H33" s="28">
         <v>0.2</v>
       </c>
-      <c r="I33" s="35">
+      <c r="I33" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>7.66</v>
       </c>
-      <c r="J33" s="29">
+      <c r="J33" s="28">
         <v>20</v>
       </c>
-      <c r="K33" s="36">
+      <c r="K33" s="35">
         <f t="shared" si="0"/>
         <v>12.34</v>
       </c>
-      <c r="L33" s="36">
+      <c r="L33" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>161.09660574412533</v>
       </c>
-      <c r="M33" s="36">
+      <c r="M33" s="35">
         <f t="shared" si="1"/>
         <v>61.7</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A34" s="20" t="s">
+      <c r="A34" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B34" s="25">
+      <c r="B34" s="24">
         <v>4.5</v>
       </c>
-      <c r="C34" s="21">
+      <c r="C34" s="20">
         <v>0.5</v>
       </c>
-      <c r="D34" s="22">
+      <c r="D34" s="21">
         <v>200</v>
       </c>
-      <c r="E34" s="27" t="s">
+      <c r="E34" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="F34" s="29">
+      <c r="F34" s="28">
         <f t="shared" si="5"/>
         <v>1.8</v>
       </c>
-      <c r="G34" s="29">
+      <c r="G34" s="28">
         <v>0.82</v>
       </c>
-      <c r="H34" s="29">
+      <c r="H34" s="28">
         <v>4</v>
       </c>
-      <c r="I34" s="35">
+      <c r="I34" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>6.62</v>
       </c>
-      <c r="J34" s="29">
+      <c r="J34" s="28">
         <v>15</v>
       </c>
-      <c r="K34" s="36">
+      <c r="K34" s="35">
         <f t="shared" si="0"/>
         <v>8.379999999999999</v>
       </c>
-      <c r="L34" s="36">
+      <c r="L34" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>126.58610271903321</v>
       </c>
-      <c r="M34" s="36">
+      <c r="M34" s="35">
         <f t="shared" si="1"/>
         <v>55.866666666666667</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="18.75" customHeight="1">
-      <c r="A35" s="20" t="s">
+      <c r="A35" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="B35" s="21"/>
-      <c r="C35" s="21">
+      <c r="B35" s="20"/>
+      <c r="C35" s="20">
         <v>0.5</v>
       </c>
-      <c r="D35" s="22">
+      <c r="D35" s="21">
         <v>185</v>
       </c>
-      <c r="E35" s="27" t="s">
+      <c r="E35" s="26" t="s">
         <v>64</v>
       </c>
-      <c r="F35" s="29">
+      <c r="F35" s="28">
         <v>2.5</v>
       </c>
-      <c r="G35" s="29">
+      <c r="G35" s="28">
         <v>0.68500000000000005</v>
       </c>
-      <c r="H35" s="29">
+      <c r="H35" s="28">
         <v>1.4</v>
       </c>
-      <c r="I35" s="35">
+      <c r="I35" s="34">
         <f>SUM(SKUTable[[#This Row],[食材成本(元/份)]:[调味成本(元/份)]])</f>
         <v>4.585</v>
       </c>
-      <c r="J35" s="29">
+      <c r="J35" s="28">
         <v>13</v>
       </c>
-      <c r="K35" s="36">
+      <c r="K35" s="35">
         <f t="shared" si="0"/>
         <v>8.4149999999999991</v>
       </c>
-      <c r="L35" s="36">
+      <c r="L35" s="35">
         <f>SKUTable[[#This Row],[毛利(元/份)]]/SKUTable[[#This Row],[总成本(元/份)]]*100</f>
         <v>183.53326063249727</v>
       </c>
-      <c r="M35" s="36">
+      <c r="M35" s="35">
         <f t="shared" si="1"/>
         <v>64.730769230769226</v>
       </c>
     </row>
     <row r="39" spans="1:13">
-      <c r="E39" s="16"/>
+      <c r="E39" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="11" type="noConversion"/>
@@ -3119,11 +3130,11 @@
       <c r="B2" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="57" t="s">
+        <v>117</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>71</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="20.100000000000001" customHeight="1">
@@ -3131,125 +3142,125 @@
         <v>69</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>74</v>
+        <v>72</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>118</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="9" t="s">
-        <v>76</v>
+      <c r="C4" s="58" t="s">
+        <v>119</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>77</v>
+        <v>72</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>120</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>70</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D6" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="C8" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="38" t="s">
+        <v>117</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>71</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A9" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>74</v>
+      <c r="C9" s="37" t="s">
+        <v>118</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D10" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="20.100000000000001" customHeight="1">
@@ -3260,30 +3271,30 @@
     </row>
     <row r="13" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="B13" s="38" t="s">
-        <v>114</v>
+        <v>84</v>
+      </c>
+      <c r="B13" s="37" t="s">
+        <v>112</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A14" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="B14" s="39" t="s">
-        <v>114</v>
+        <v>86</v>
+      </c>
+      <c r="B14" s="38" t="s">
+        <v>112</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="20.100000000000001" customHeight="1">
@@ -3294,58 +3305,58 @@
     </row>
     <row r="16" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A16" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="D16" s="8" t="s">
         <v>90</v>
-      </c>
-      <c r="C16" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A17" s="5" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="20.100000000000001" customHeight="1">
@@ -3353,41 +3364,41 @@
         <v>45</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A21" s="5" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A22" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D22" s="8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="20.100000000000001" customHeight="1">
@@ -3398,72 +3409,72 @@
     </row>
     <row r="24" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A24" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="B24" s="8" t="s">
+      <c r="D24" s="8" t="s">
         <v>101</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A25" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B25" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="D25" s="6" t="s">
         <v>101</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A26" s="7" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A27" s="5" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A28" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C28" s="8" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D28" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="29" spans="1:4" ht="20.100000000000001" customHeight="1">
@@ -3471,13 +3482,13 @@
         <v>22</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:4" ht="20.100000000000001" customHeight="1">
@@ -3485,13 +3496,13 @@
         <v>19</v>
       </c>
       <c r="B30" s="8" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C30" s="8" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="20.100000000000001" customHeight="1">
@@ -3499,13 +3510,13 @@
         <v>17</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>

--- a/财务与流水/馋唻买-听涛路店商品表 - 调价.xlsx
+++ b/财务与流水/馋唻买-听涛路店商品表 - 调价.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github localpath\ChanWeiMai\财务与流水\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E1FE97-8212-43F1-9CE1-15D481BE8461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC4B9883-5996-49C7-9F5E-45EC6EA3C26C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2475" yWindow="885" windowWidth="35070" windowHeight="19335" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1980" yWindow="900" windowWidth="35070" windowHeight="19335" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="堂食利润" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="120">
   <si>
     <t>SKU</t>
   </si>
@@ -248,9 +248,6 @@
     <t>肉筋瘦肉丸</t>
   </si>
   <si>
-    <t>12元</t>
-  </si>
-  <si>
     <t>牛肉羹瘦肉丸</t>
   </si>
   <si>
@@ -294,12 +291,6 @@
   </si>
   <si>
     <t>特色口味</t>
-  </si>
-  <si>
-    <t>手工挂面+瘦肉丸</t>
-  </si>
-  <si>
-    <t>月240克</t>
   </si>
   <si>
     <t>火鸡面干拌瘦肉丸(辣)</t>
@@ -392,6 +383,14 @@
   </si>
   <si>
     <t>18元</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>特色口味</t>
+    <phoneticPr fontId="11" type="noConversion"/>
+  </si>
+  <si>
+    <t>本店招牌</t>
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
 </sst>
@@ -2368,7 +2367,7 @@
     </row>
     <row r="20" spans="1:13" ht="18.75" customHeight="1">
       <c r="A20" s="39" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B20" s="20">
         <v>18</v>
@@ -2527,7 +2526,7 @@
     </row>
     <row r="24" spans="1:13" ht="18.75" customHeight="1">
       <c r="A24" s="39" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B24" s="20">
         <v>8</v>
@@ -2842,7 +2841,7 @@
     </row>
     <row r="31" spans="1:13" ht="18.75" customHeight="1">
       <c r="A31" s="47" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="B31" s="20"/>
       <c r="C31" s="20">
@@ -2883,7 +2882,7 @@
     </row>
     <row r="32" spans="1:13" ht="18.75" customHeight="1">
       <c r="A32" s="48" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B32" s="49"/>
       <c r="C32" s="49">
@@ -3102,7 +3101,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr defaultColWidth="30.75" defaultRowHeight="20.100000000000001" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="36.25" customWidth="1"/>
@@ -3131,7 +3130,7 @@
         <v>70</v>
       </c>
       <c r="C2" s="57" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>71</v>
@@ -3145,7 +3144,7 @@
         <v>72</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>71</v>
@@ -3159,7 +3158,7 @@
         <v>70</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="D4" s="8" t="s">
         <v>71</v>
@@ -3173,7 +3172,7 @@
         <v>72</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>71</v>
@@ -3181,7 +3180,7 @@
     </row>
     <row r="6" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>70</v>
@@ -3195,13 +3194,13 @@
     </row>
     <row r="7" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A7" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>72</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>71</v>
@@ -3209,13 +3208,13 @@
     </row>
     <row r="8" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A8" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B8" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B8" s="8" t="s">
-        <v>79</v>
-      </c>
       <c r="C8" s="38" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>71</v>
@@ -3223,38 +3222,38 @@
     </row>
     <row r="9" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A9" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" s="37" t="s">
-        <v>118</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>71</v>
+        <v>115</v>
+      </c>
+      <c r="D9" s="37" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>71</v>
+        <v>88</v>
+      </c>
+      <c r="D10" s="38" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A11" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C11" s="6" t="s">
         <v>73</v>
@@ -3271,30 +3270,30 @@
     </row>
     <row r="13" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A13" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" s="37" t="s">
+        <v>109</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>84</v>
-      </c>
-      <c r="B13" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A14" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B14" s="38" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="20.100000000000001" customHeight="1">
@@ -3305,218 +3304,204 @@
     </row>
     <row r="16" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A16" s="7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="C16" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>89</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A17" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="C17" s="6" t="s">
-        <v>75</v>
-      </c>
       <c r="D17" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A18" s="7" t="s">
-        <v>93</v>
+        <v>45</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D18" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A19" s="5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="20.100000000000001" customHeight="1">
       <c r="A20" s="7" t="s">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="D20" s="8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="20.100000000000001" customHeight="1">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" s="38" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="A22" s="5"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6"/>
+      <c r="D22" s="6"/>
+    </row>
+    <row r="23" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="A23" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B23" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="20.100000000000001" customHeight="1">
-      <c r="A22" s="7" t="s">
+      <c r="C23" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="B22" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="20.100000000000001" customHeight="1">
-      <c r="A23" s="5"/>
-      <c r="B23" s="6"/>
-      <c r="C23" s="6"/>
-      <c r="D23" s="6"/>
+      <c r="D23" s="8" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="24" spans="1:4" ht="20.100000000000001" customHeight="1">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B24" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="C24" s="8" t="s">
+    </row>
+    <row r="25" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="A25" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="D24" s="8" t="s">
+      <c r="B25" s="8" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="25" spans="1:4" ht="20.100000000000001" customHeight="1">
-      <c r="A25" s="5" t="s">
+      <c r="C25" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="A26" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="C25" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="D25" s="6" t="s">
+      <c r="B26" s="6" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" ht="20.100000000000001" customHeight="1">
-      <c r="A26" s="7" t="s">
+      <c r="C26" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="A27" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B27" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="C26" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="20.100000000000001" customHeight="1">
-      <c r="A27" s="5" t="s">
+      <c r="C27" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="A28" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B28" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" ht="20.100000000000001" customHeight="1">
-      <c r="A28" s="7" t="s">
+      <c r="C28" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="A29" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C29" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="B28" s="8" t="s">
+      <c r="D29" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" ht="20.100000000000001" customHeight="1">
+      <c r="A30" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="C28" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" ht="20.100000000000001" customHeight="1">
-      <c r="A29" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B29" s="6" t="s">
+      <c r="C30" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="C29" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" ht="20.100000000000001" customHeight="1">
-      <c r="A30" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B30" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="C30" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" ht="20.100000000000001" customHeight="1">
-      <c r="A31" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="C31" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>101</v>
+      <c r="D30" s="6" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>

--- a/财务与流水/馋唻买-听涛路店商品表 - 调价.xlsx
+++ b/财务与流水/馋唻买-听涛路店商品表 - 调价.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github localpath\ChanWeiMai\财务与流水\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC4B9883-5996-49C7-9F5E-45EC6EA3C26C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{456931E6-AEF3-4DDA-9BCC-AB98AAF099B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1980" yWindow="900" windowWidth="35070" windowHeight="19335" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2160" yWindow="1545" windowWidth="35070" windowHeight="19335" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="堂食利润" sheetId="1" r:id="rId1"/>
